--- a/artfynd/A 47647-2022 artfynd.xlsx
+++ b/artfynd/A 47647-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 47647-2022 artfynd.xlsx
+++ b/artfynd/A 47647-2022 artfynd.xlsx
@@ -2039,7 +2039,7 @@
         <v>104488181</v>
       </c>
       <c r="B14" t="n">
-        <v>12555</v>
+        <v>12558</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 47647-2022 artfynd.xlsx
+++ b/artfynd/A 47647-2022 artfynd.xlsx
@@ -2039,7 +2039,7 @@
         <v>104488181</v>
       </c>
       <c r="B14" t="n">
-        <v>12558</v>
+        <v>12555</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 47647-2022 artfynd.xlsx
+++ b/artfynd/A 47647-2022 artfynd.xlsx
@@ -2039,7 +2039,7 @@
         <v>104488181</v>
       </c>
       <c r="B14" t="n">
-        <v>12555</v>
+        <v>12558</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>0</v>
       </c>
       <c r="AE14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">

--- a/artfynd/A 47647-2022 artfynd.xlsx
+++ b/artfynd/A 47647-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104484678</v>
+        <v>104486586</v>
       </c>
       <c r="B2" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>602932.8008378254</v>
+        <v>602860</v>
       </c>
       <c r="R2" t="n">
-        <v>7020432.544296024</v>
+        <v>7020363</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,19 +744,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,15 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104485529</v>
+        <v>104484678</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,21 +784,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +809,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602865.5745604448</v>
+        <v>602932</v>
       </c>
       <c r="R3" t="n">
-        <v>7020378.635281698</v>
+        <v>7020433</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,19 +842,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,15 +871,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104486728</v>
+        <v>104486014</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,21 +882,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +907,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>602844.1700356446</v>
+        <v>602868</v>
       </c>
       <c r="R4" t="n">
-        <v>7020385.601249047</v>
+        <v>7020353</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -975,19 +940,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,37 +969,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104486004</v>
+        <v>104488361</v>
       </c>
       <c r="B5" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>602867.7598707876</v>
+        <v>602861</v>
       </c>
       <c r="R5" t="n">
-        <v>7020352.601639125</v>
+        <v>7020361</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1088,19 +1038,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,15 +1067,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104489214</v>
+        <v>104488382</v>
       </c>
       <c r="B6" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1152,12 +1087,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>602935.874117066</v>
+        <v>602841</v>
       </c>
       <c r="R6" t="n">
-        <v>7020519.50184454</v>
+        <v>7020369</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1201,19 +1136,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,15 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104488382</v>
+        <v>104489214</v>
       </c>
       <c r="B7" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,12 +1185,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1281,10 +1201,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>602840.6360825889</v>
+        <v>602935</v>
       </c>
       <c r="R7" t="n">
-        <v>7020369.285999824</v>
+        <v>7020520</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1314,19 +1234,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1353,15 +1263,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104486823</v>
+        <v>104484834</v>
       </c>
       <c r="B8" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,21 +1274,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1394,10 +1299,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>602834.9618700986</v>
+        <v>602912</v>
       </c>
       <c r="R8" t="n">
-        <v>7020335.349671371</v>
+        <v>7020436</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1427,19 +1332,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,15 +1361,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104484834</v>
+        <v>104486004</v>
       </c>
       <c r="B9" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1482,21 +1372,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1507,10 +1397,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>602911.4972840565</v>
+        <v>602868</v>
       </c>
       <c r="R9" t="n">
-        <v>7020436.36255259</v>
+        <v>7020353</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1540,19 +1430,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1579,37 +1459,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104486014</v>
+        <v>104485529</v>
       </c>
       <c r="B10" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1620,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>602867.7598707876</v>
+        <v>602866</v>
       </c>
       <c r="R10" t="n">
-        <v>7020352.601639125</v>
+        <v>7020379</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1653,19 +1528,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,56 +1557,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104486779</v>
+        <v>104486728</v>
       </c>
       <c r="B11" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>602843.0124338201</v>
+        <v>602845</v>
       </c>
       <c r="R11" t="n">
-        <v>7020351.359548277</v>
+        <v>7020386</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1771,19 +1626,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,37 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104488361</v>
+        <v>104486823</v>
       </c>
       <c r="B12" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1851,10 +1691,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>602860.7476253243</v>
+        <v>602835</v>
       </c>
       <c r="R12" t="n">
-        <v>7020360.478333115</v>
+        <v>7020335</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1884,19 +1724,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1923,15 +1753,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>104486586</v>
+        <v>104489941</v>
       </c>
       <c r="B13" t="n">
-        <v>89338</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1939,21 +1764,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>112</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1964,10 +1789,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>602859.77524807</v>
+        <v>602889</v>
       </c>
       <c r="R13" t="n">
-        <v>7020362.697523143</v>
+        <v>7020604</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1997,19 +1822,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2039,7 +1854,7 @@
         <v>104488181</v>
       </c>
       <c r="B14" t="n">
-        <v>12558</v>
+        <v>12566</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2142,6 +1957,109 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>104486779</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>602843</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7020352</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-11-05</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-11-05</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47647-2022 artfynd.xlsx
+++ b/artfynd/A 47647-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104486586</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104484678</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -966,6 +981,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104486014</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104488361</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104488382</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1260,6 +1290,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104489214</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1358,6 +1393,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104484834</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1456,6 +1496,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104486004</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1554,6 +1599,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104485529</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1652,6 +1702,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104486728</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1750,6 +1805,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104486823</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1848,6 +1908,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104489941</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1956,6 +2021,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104488181</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2059,8 +2129,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104486779</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>